--- a/submissions/03-pretreatment-smr-q3-2026/inputs/lab_results_apr_sep2026.xlsx
+++ b/submissions/03-pretreatment-smr-q3-2026/inputs/lab_results_apr_sep2026.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2798C0DA-AB0C-CA48-9E8D-D31B05D36DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C56D408-7199-8044-8669-C9C940B05B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="153">
   <si>
     <t>Great Lakes Analytical Laboratories - analytical results, client Vandeveer Plating LLC, sampling point Outfall 001 (pretreatment system effluent)</t>
   </si>
   <si>
-    <t>Results in mg/L. Qualifiers: NS = not sampled; U = not detected at the MDL shown on the Methods tab; J = detected between the MDL and the reporting limit, value estimated; H = holding time exceeded, result not valid for compliance use. Compiled from lab reports GLA-26-1187 through GLA-26-1904.</t>
+    <t>Results in mg/L. Qualifiers: NS = not sampled; U = not detected at the MDL shown on the Methods tab; J = detected between the MDL and the reporting limit, value estimated. Compiled from lab reports GLA-26-1187 through GLA-26-1904.</t>
   </si>
   <si>
     <t>SAMPLE ID</t>
@@ -163,7 +163,7 @@
     <t>07/07/2026</t>
   </si>
   <si>
-    <t>07/17/2026</t>
+    <t>08/07/2026</t>
   </si>
   <si>
     <t>VP-260721</t>
@@ -193,9 +193,6 @@
     <t>08/25/2026</t>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
     <t>09/04/2026</t>
   </si>
   <si>
@@ -322,22 +319,25 @@
     <t>06/17/2026</t>
   </si>
   <si>
-    <t>06/20/2026</t>
+    <t>07/13/2026</t>
   </si>
   <si>
     <t>06/18/2026</t>
   </si>
   <si>
+    <t>Metals run held for the ICP-OES torch repair; digested 06/19, analyzed 07/13</t>
+  </si>
+  <si>
     <t>07/07/2026 06:40</t>
   </si>
   <si>
     <t>07/08/2026</t>
   </si>
   <si>
-    <t>07/12/2026</t>
-  </si>
-  <si>
-    <t>07/13/2026</t>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Metals digestate lost on the 07/12 run; re-digested from the retained aliquot and analyzed 08/06; report GLA-26-1611 issued 08/07 with the cyanide</t>
   </si>
   <si>
     <t>07/21/2026 06:30</t>
@@ -376,7 +376,7 @@
     <t>08/27/2026</t>
   </si>
   <si>
-    <t>Nickel digestate lost in instrument fault 08/29; re-digested and analyzed 09/28, beyond the 28-day metals holding period; nickel result qualified H</t>
+    <t>Nickel digestate lost in the instrument fault of 08/29; re-digested from the retained aliquot and nickel analyzed 09/28</t>
   </si>
   <si>
     <t>09/09/2026 06:40</t>
@@ -388,6 +388,9 @@
     <t>09/12/2026</t>
   </si>
   <si>
+    <t>Cyanide distillation repeated 09/22 after the 09/12 spike recovery failed</t>
+  </si>
+  <si>
     <t>09/22/2026 06:35</t>
   </si>
   <si>
@@ -412,7 +415,7 @@
     <t>Resample requested by client after the 09/09 event; cyanide grab not collected, metals only</t>
   </si>
   <si>
-    <t>Holding periods applied by the laboratory: 28 days for total metals (preserved), 14 days for total cyanide (preserved), field pH at collection.</t>
+    <t>Holding periods under 40 CFR Part 136 as the laboratory tracks them: 28 days from collection for total metals (preserved), 14 days for total cyanide (preserved); field pH at collection.</t>
   </si>
   <si>
     <t>Methods, detection limits and reporting limits</t>
@@ -877,7 +880,7 @@
     <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1198,7 @@
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="4">
-        <v>4.08</v>
+        <v>3.97</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="4">
@@ -1383,9 +1386,7 @@
       <c r="K14" s="4">
         <v>1.9</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="L14" s="2"/>
       <c r="M14" s="4">
         <v>1.18</v>
       </c>
@@ -1398,15 +1399,15 @@
         <v>7.5</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>22</v>
@@ -1442,15 +1443,15 @@
         <v>7.9</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>28</v>
@@ -1488,21 +1489,21 @@
         <v>7.3</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="E17" s="4">
         <v>0.005</v>
@@ -1527,18 +1528,18 @@
       </c>
       <c r="N17" s="2"/>
       <c r="P17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q17" s="5">
         <v>7.4</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1560,9 +1561,9 @@
     <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1573,19 +1574,19 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -1593,16 +1594,16 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="F4" s="2">
         <v>5</v>
@@ -1614,16 +1615,16 @@
         <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F5" s="2">
         <v>2</v>
@@ -1635,16 +1636,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1656,22 +1657,22 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1679,44 +1680,46 @@
         <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
       </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G9" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
@@ -1730,12 +1733,14 @@
         <v>105</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -1779,7 +1784,7 @@
       </c>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>56</v>
       </c>
@@ -1804,7 +1809,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>120</v>
@@ -1816,58 +1821,60 @@
         <v>122</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2">
-        <v>3</v>
-      </c>
-      <c r="G14" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1885,34 +1892,34 @@
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C4" s="4">
         <v>0.005</v>
@@ -1921,15 +1928,15 @@
         <v>0.01</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4">
         <v>0.01</v>
@@ -1938,15 +1945,15 @@
         <v>0.02</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C6" s="4">
         <v>0.01</v>
@@ -1955,15 +1962,15 @@
         <v>0.02</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="4">
         <v>0.02</v>
@@ -1972,15 +1979,15 @@
         <v>0.04</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" s="4">
         <v>0.02</v>
@@ -1989,15 +1996,15 @@
         <v>0.04</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C9" s="4">
         <v>0.005</v>
@@ -2006,24 +2013,24 @@
         <v>0.01</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/03-pretreatment-smr-q3-2026/inputs/lab_results_apr_sep2026.xlsx
+++ b/submissions/03-pretreatment-smr-q3-2026/inputs/lab_results_apr_sep2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C56D408-7199-8044-8669-C9C940B05B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8102E112-9A77-E349-BE58-079FDE6CD213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/submissions/03-pretreatment-smr-q3-2026/inputs/lab_results_apr_sep2026.xlsx
+++ b/submissions/03-pretreatment-smr-q3-2026/inputs/lab_results_apr_sep2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069DFD29-7AC7-C548-B1C5-90802F1870D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E7699-5578-0947-A82F-83CA648E0E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="199">
   <si>
     <t>Great Lakes Analytical Laboratories - analytical results, client Vandeveer Plating LLC, Wyoming, Michigan</t>
   </si>
@@ -241,9 +241,6 @@
     <t>09/09/2026</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
     <t>GLA-26-1811</t>
   </si>
   <si>
@@ -277,7 +274,7 @@
     <t>Chain of custody and analysis log</t>
   </si>
   <si>
-    <t>COLLECTED, SAMPLED AT and SAMPLE are as the client wrote them on the chain of custody. REPORT ISSUED is the time the first numbered report went to the client and to the City.</t>
+    <t>COLLECTED, SAMPLED AT and SAMPLE are as the client wrote them on the chain of custody; for a composite, COLLECTED is the end of the 24-hour composite period. METALS ANALYZED and CYANIDE ANALYZED are the start of each analysis. REPORT ISSUED is the time the first numbered report went to the client and to the City.</t>
   </si>
   <si>
     <t>SAMPLED AT</t>
@@ -298,9 +295,6 @@
     <t>REPORT ISSUED</t>
   </si>
   <si>
-    <t>LAB NOTE</t>
-  </si>
-  <si>
     <t>03/31/2026 06:45</t>
   </si>
   <si>
@@ -313,10 +307,10 @@
     <t>04/01/2026</t>
   </si>
   <si>
-    <t>04/03/2026</t>
-  </si>
-  <si>
-    <t>04/04/2026</t>
+    <t>04/03/2026 13:20</t>
+  </si>
+  <si>
+    <t>04/04/2026 09:15</t>
   </si>
   <si>
     <t>04/09/2026 10:20</t>
@@ -328,28 +322,25 @@
     <t>04/08/2026</t>
   </si>
   <si>
-    <t>05/14/2026</t>
-  </si>
-  <si>
-    <t>04/12/2026</t>
+    <t>05/14/2026 11:05</t>
+  </si>
+  <si>
+    <t>04/12/2026 10:30</t>
   </si>
   <si>
     <t>05/15/2026 10:40</t>
   </si>
   <si>
-    <t>Metals held for the ICP-OES torch repair; report held for the metals</t>
-  </si>
-  <si>
     <t>04/21/2026 06:35</t>
   </si>
   <si>
     <t>04/22/2026</t>
   </si>
   <si>
-    <t>04/25/2026</t>
-  </si>
-  <si>
-    <t>04/23/2026</t>
+    <t>04/25/2026 09:40</t>
+  </si>
+  <si>
+    <t>04/23/2026 14:05</t>
   </si>
   <si>
     <t>04/30/2026 15:05</t>
@@ -361,43 +352,40 @@
     <t>05/06/2026</t>
   </si>
   <si>
-    <t>05/08/2026</t>
+    <t>05/08/2026 10:50</t>
+  </si>
+  <si>
+    <t>05/19/2026 06:30</t>
   </si>
   <si>
     <t>05/20/2026 09:15</t>
   </si>
   <si>
-    <t>Cyanide still down for a condenser; distilled and analyzed 05/19</t>
-  </si>
-  <si>
     <t>05/19/2026 06:45</t>
   </si>
   <si>
     <t>05/20/2026</t>
   </si>
   <si>
-    <t>05/26/2026</t>
-  </si>
-  <si>
-    <t>05/25/2026</t>
+    <t>05/26/2026 13:15</t>
+  </si>
+  <si>
+    <t>05/25/2026 09:20</t>
   </si>
   <si>
     <t>05/29/2026 13:30</t>
   </si>
   <si>
-    <t>Cyanide detected below the reporting limit; result qualified J</t>
-  </si>
-  <si>
     <t>06/02/2026 06:40</t>
   </si>
   <si>
     <t>06/03/2026</t>
   </si>
   <si>
-    <t>06/08/2026</t>
-  </si>
-  <si>
-    <t>06/07/2026</t>
+    <t>06/08/2026 11:30</t>
+  </si>
+  <si>
+    <t>06/07/2026 10:10</t>
   </si>
   <si>
     <t>06/12/2026 11:10</t>
@@ -409,10 +397,10 @@
     <t>06/17/2026</t>
   </si>
   <si>
-    <t>06/20/2026</t>
-  </si>
-  <si>
-    <t>06/18/2026</t>
+    <t>06/20/2026 09:55</t>
+  </si>
+  <si>
+    <t>06/18/2026 14:40</t>
   </si>
   <si>
     <t>06/26/2026 09:50</t>
@@ -424,10 +412,10 @@
     <t>07/08/2026</t>
   </si>
   <si>
-    <t>07/11/2026</t>
-  </si>
-  <si>
-    <t>07/13/2026</t>
+    <t>07/11/2026 14:10</t>
+  </si>
+  <si>
+    <t>07/13/2026 10:25</t>
   </si>
   <si>
     <t>07/16/2026 14:45</t>
@@ -439,10 +427,10 @@
     <t>07/22/2026</t>
   </si>
   <si>
-    <t>07/26/2026</t>
-  </si>
-  <si>
-    <t>07/25/2026</t>
+    <t>07/26/2026 10:40</t>
+  </si>
+  <si>
+    <t>08/04/2026 10:20</t>
   </si>
   <si>
     <t>07/30/2026 14:05</t>
@@ -454,76 +442,67 @@
     <t>08/12/2026</t>
   </si>
   <si>
-    <t>08/15/2026</t>
+    <t>08/15/2026 09:30</t>
+  </si>
+  <si>
+    <t>08/26/2026 13:50</t>
+  </si>
+  <si>
+    <t>08/27/2026 09:30</t>
+  </si>
+  <si>
+    <t>08/18/2026 06:40</t>
+  </si>
+  <si>
+    <t>08/20/2026</t>
+  </si>
+  <si>
+    <t>08/23/2026 11:15</t>
+  </si>
+  <si>
+    <t>08/24/2026 10:05</t>
+  </si>
+  <si>
+    <t>08/26/2026 15:40</t>
+  </si>
+  <si>
+    <t>08/19/2026 07:10</t>
+  </si>
+  <si>
+    <t>Clar. weir</t>
+  </si>
+  <si>
+    <t>Grab</t>
+  </si>
+  <si>
+    <t>not collected</t>
+  </si>
+  <si>
+    <t>08/25/2026 06:50</t>
   </si>
   <si>
     <t>08/26/2026</t>
   </si>
   <si>
-    <t>08/27/2026 09:30</t>
-  </si>
-  <si>
-    <t>Cyanide distillation repeated 08/26 after the 08/14 spike recovery failed; report held for the cyanide</t>
-  </si>
-  <si>
-    <t>08/18/2026 06:40</t>
-  </si>
-  <si>
-    <t>08/20/2026</t>
-  </si>
-  <si>
-    <t>08/23/2026</t>
-  </si>
-  <si>
-    <t>08/24/2026</t>
-  </si>
-  <si>
-    <t>08/26/2026 15:40</t>
-  </si>
-  <si>
-    <t>Extra sample at the client's request</t>
-  </si>
-  <si>
-    <t>08/19/2026 07:10</t>
-  </si>
-  <si>
-    <t>Clar. weir</t>
-  </si>
-  <si>
-    <t>Grab</t>
-  </si>
-  <si>
-    <t>not collected</t>
-  </si>
-  <si>
-    <t>Client's grab for the copper work, 500 mL bottle, metals only</t>
-  </si>
-  <si>
-    <t>08/25/2026 06:50</t>
-  </si>
-  <si>
-    <t>08/29/2026</t>
-  </si>
-  <si>
-    <t>08/27/2026</t>
+    <t>08/29/2026 10:35</t>
+  </si>
+  <si>
+    <t>08/27/2026 09:45</t>
   </si>
   <si>
     <t>09/04/2026 13:15</t>
   </si>
   <si>
-    <t>Revision 1 issued after the first report</t>
-  </si>
-  <si>
-    <t>09/09/2026 09:00</t>
+    <t>09/09/2026 06:40</t>
   </si>
   <si>
     <t>09/10/2026</t>
   </si>
   <si>
-    <t>09/12/2026</t>
-  </si>
-  <si>
-    <t>09/14/2026</t>
+    <t>09/12/2026 13:40</t>
+  </si>
+  <si>
+    <t>09/14/2026 10:30</t>
   </si>
   <si>
     <t>09/15/2026 11:20</t>
@@ -532,10 +511,10 @@
     <t>09/22/2026 06:35</t>
   </si>
   <si>
-    <t>09/29/2026</t>
-  </si>
-  <si>
-    <t>09/28/2026</t>
+    <t>09/29/2026 09:50</t>
+  </si>
+  <si>
+    <t>09/28/2026 14:15</t>
   </si>
   <si>
     <t>10/01/2026 10:05</t>
@@ -550,16 +529,13 @@
     <t>09/24/2026</t>
   </si>
   <si>
-    <t>09/26/2026</t>
-  </si>
-  <si>
-    <t>Resample requested by client after the 09/09 event; cyanide grab not collected, metals only</t>
+    <t>09/26/2026 11:20</t>
   </si>
   <si>
     <t>Methods, detection limits, reporting limits and holding times</t>
   </si>
   <si>
-    <t>Holding times run from the time of collection to analysis, 40 CFR Part 136, Table II.</t>
+    <t>Holding times run in elapsed hours from the time shown as collected on the chain of custody to the start of the analysis, 40 CFR Part 136, Table II. For a composite, collected is the end of the 24-hour composite period; for a grab, the time the grab was taken.</t>
   </si>
   <si>
     <t>PARAMETER</t>
@@ -708,7 +684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -716,9 +692,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1651,7 +1624,7 @@
         <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>23</v>
@@ -1674,19 +1647,22 @@
       <c r="O18" s="4">
         <v>0.41</v>
       </c>
+      <c r="P18" t="s">
+        <v>37</v>
+      </c>
       <c r="Q18" s="6">
         <v>7.9</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>32</v>
@@ -1719,21 +1695,21 @@
         <v>7.3</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E20" s="4">
         <v>0.005</v>
@@ -1761,12 +1737,12 @@
         <v>7.4</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1776,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1784,24 +1760,23 @@
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1809,516 +1784,489 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>52</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>63</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="H19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F18" s="2" t="s">
+    </row>
+    <row r="20" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2340,43 +2288,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C5" s="4">
         <v>0.005</v>
@@ -2385,21 +2333,21 @@
         <v>0.01</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C6" s="4">
         <v>0.01</v>
@@ -2408,21 +2356,21 @@
         <v>0.02</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C7" s="4">
         <v>0.01</v>
@@ -2431,21 +2379,21 @@
         <v>0.02</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C8" s="4">
         <v>0.02</v>
@@ -2454,21 +2402,21 @@
         <v>0.04</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C9" s="4">
         <v>0.02</v>
@@ -2477,21 +2425,21 @@
         <v>0.04</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C10" s="4">
         <v>0.005</v>
@@ -2500,36 +2448,36 @@
         <v>0.01</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
